--- a/public/fun/pack/xlsx/quote/견적서_06_인테리어·시공_봄비내리는창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_06_인테리어·시공_봄비내리는창가.xlsx
@@ -25,7 +25,7 @@
     <t>인테리어·시공 견적서</t>
   </si>
   <si>
-    <t>“비 오는 날에도 약속은 변하지 않습니다”</t>
+    <t>“납품 일정까지 한 장에 정리했습니다”</t>
   </si>
   <si>
     <t>봄비 내리는 창가 테마</t>
@@ -203,7 +203,7 @@
 • 결제: 계약금 30% / 중도금 40% / 잔금 30%(공사 완료 후)</t>
   </si>
   <si>
-    <t>믿고 맡겨 주셔서 감사합니다.  ·  비 오는 날에도 약속은 변하지 않습니다</t>
+    <t>믿고 맡겨 주셔서 감사합니다.  ·  납품 일정까지 한 장에 정리했습니다</t>
   </si>
 </sst>
 </file>

--- a/public/fun/pack/xlsx/quote/견적서_06_인테리어·시공_봄비내리는창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_06_인테리어·시공_봄비내리는창가.xlsx
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
   <si>
     <t>인테리어·시공 견적서</t>
-  </si>
-  <si>
-    <t>“납품 일정까지 한 장에 정리했습니다”</t>
   </si>
   <si>
     <t>봄비 내리는 창가 테마</t>
@@ -203,7 +200,7 @@
 • 결제: 계약금 30% / 중도금 40% / 잔금 30%(공사 완료 후)</t>
   </si>
   <si>
-    <t>믿고 맡겨 주셔서 감사합니다.  ·  납품 일정까지 한 장에 정리했습니다</t>
+    <t>믿고 맡겨 주셔서 감사합니다.</t>
   </si>
 </sst>
 </file>
@@ -859,7 +856,7 @@
     <row r="1" spans="2:8" ht="14" customHeight="1"/>
     <row r="2" spans="2:8" ht="40" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -869,9 +866,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -881,12 +876,12 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -894,12 +889,12 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -907,7 +902,7 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5">
         <f>TODAY()</f>
@@ -915,7 +910,7 @@
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -923,7 +918,7 @@
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="6">
         <v>30</v>
@@ -933,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -941,14 +936,14 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -956,7 +951,7 @@
     </row>
     <row r="10" spans="2:8" ht="32" customHeight="1">
       <c r="B10" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="9">
@@ -970,25 +965,25 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="G12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -996,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1023,7 +1018,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1050,7 +1045,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1077,7 +1072,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
@@ -1354,7 +1349,7 @@
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -1368,7 +1363,7 @@
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1381,7 +1376,7 @@
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -1395,13 +1390,13 @@
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="16">
@@ -1411,7 +1406,7 @@
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -1425,10 +1420,10 @@
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>59</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -1462,7 +1457,7 @@
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
@@ -1531,7 +1526,7 @@
   <sheetData>
     <row r="1" spans="2:5">
       <c r="B1" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -1539,27 +1534,27 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="E4" s="15">
         <v>26200</v>
@@ -1567,13 +1562,13 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="21" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="15">
         <v>47200</v>
@@ -1581,13 +1576,13 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="15">
         <v>63000</v>
@@ -1595,13 +1590,13 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="E7" s="15">
         <v>9400</v>
@@ -1609,13 +1604,13 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="21" t="s">
         <v>29</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>30</v>
       </c>
       <c r="E8" s="15">
         <v>315000</v>
@@ -1623,13 +1618,13 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="21" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="E9" s="15">
         <v>157500</v>
@@ -1637,13 +1632,13 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>30</v>
       </c>
       <c r="E10" s="15">
         <v>210000</v>
@@ -1651,13 +1646,13 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="E11" s="15">
         <v>12600</v>
@@ -1824,71 +1819,69 @@
       <c r="C2" s="26"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="27" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="27"/>
       <c r="C3" s="27"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="28"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1">
       <c r="B7" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="22" customHeight="1">
       <c r="B9" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="32" customHeight="1">
       <c r="B10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="28" customHeight="1">
       <c r="B12" s="33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="33"/>
     </row>
     <row r="13" spans="2:3" ht="28" customHeight="1">
       <c r="B13" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="33"/>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="34"/>
     </row>

--- a/public/fun/pack/xlsx/quote/견적서_06_인테리어·시공_봄비내리는창가.xlsx
+++ b/public/fun/pack/xlsx/quote/견적서_06_인테리어·시공_봄비내리는창가.xlsx
@@ -956,7 +956,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="9">
         <f>H32</f>
-        <v>0</v>
+        <v>763840</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -993,24 +993,24 @@
       <c r="C13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>㎡당</v>
       </c>
       <c r="E13" s="13">
         <v>2</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>㎡</v>
       </c>
       <c r="G13" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C13,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>26200</v>
       </c>
       <c r="H13" s="16">
         <f>IF(OR(E13="",G13=""),"",E13*G13)</f>
-        <v>0</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -1020,24 +1020,24 @@
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>LED 1구</v>
       </c>
       <c r="E14" s="13">
         <v>4</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>개</v>
       </c>
       <c r="G14" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C14,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>47200</v>
       </c>
       <c r="H14" s="16">
         <f>IF(OR(E14="",G14=""),"",E14*G14)</f>
-        <v>0</v>
+        <v>188800</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -1047,24 +1047,24 @@
       <c r="C15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>㎡당</v>
       </c>
       <c r="E15" s="13">
         <v>6</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>㎡</v>
       </c>
       <c r="G15" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C15,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="H15" s="16">
         <f>IF(OR(E15="",G15=""),"",E15*G15)</f>
-        <v>0</v>
+        <v>378000</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -1074,24 +1074,24 @@
       <c r="C16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="12" t="str">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>㎡당</v>
       </c>
       <c r="E16" s="13">
         <v>8</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="14" t="str">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>㎡</v>
       </c>
       <c r="G16" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C16,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="H16" s="16">
         <f>IF(OR(E16="",G16=""),"",E16*G16)</f>
-        <v>0</v>
+        <v>75200</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -1101,20 +1101,20 @@
       <c r="C17" s="4"/>
       <c r="D17" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C17,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C17,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G17" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C17,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H17" s="16">
         <f>IF(OR(E17="",G17=""),"",E17*G17)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -1124,20 +1124,20 @@
       <c r="C18" s="4"/>
       <c r="D18" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C18,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C18,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G18" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C18,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H18" s="16">
         <f>IF(OR(E18="",G18=""),"",E18*G18)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -1147,20 +1147,20 @@
       <c r="C19" s="4"/>
       <c r="D19" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C19,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C19,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G19" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C19,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H19" s="16">
         <f>IF(OR(E19="",G19=""),"",E19*G19)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -1170,20 +1170,20 @@
       <c r="C20" s="4"/>
       <c r="D20" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C20,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C20,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G20" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C20,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H20" s="16">
         <f>IF(OR(E20="",G20=""),"",E20*G20)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -1193,20 +1193,20 @@
       <c r="C21" s="4"/>
       <c r="D21" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C21,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C21,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G21" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C21,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H21" s="16">
         <f>IF(OR(E21="",G21=""),"",E21*G21)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -1216,20 +1216,20 @@
       <c r="C22" s="4"/>
       <c r="D22" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C22,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C22,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G22" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C22,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H22" s="16">
         <f>IF(OR(E22="",G22=""),"",E22*G22)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -1239,20 +1239,20 @@
       <c r="C23" s="4"/>
       <c r="D23" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C23,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C23,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G23" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C23,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H23" s="16">
         <f>IF(OR(E23="",G23=""),"",E23*G23)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -1262,20 +1262,20 @@
       <c r="C24" s="4"/>
       <c r="D24" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C24,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C24,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G24" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C24,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H24" s="16">
         <f>IF(OR(E24="",G24=""),"",E24*G24)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -1285,20 +1285,20 @@
       <c r="C25" s="4"/>
       <c r="D25" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C25,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C25,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G25" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C25,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H25" s="16">
         <f>IF(OR(E25="",G25=""),"",E25*G25)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -1308,20 +1308,20 @@
       <c r="C26" s="4"/>
       <c r="D26" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C26,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C26,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G26" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C26,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H26" s="16">
         <f>IF(OR(E26="",G26=""),"",E26*G26)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -1331,20 +1331,20 @@
       <c r="C27" s="4"/>
       <c r="D27" s="12">
         <f>IFERROR(INDEX('단가표'!$C$4:$C$33,MATCH(C27,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14">
         <f>IFERROR(INDEX('단가표'!$D$4:$D$33,MATCH(C27,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G27" s="15">
         <f>IFERROR(INDEX('단가표'!$E$4:$E$33,MATCH(C27,'단가표'!$B$4:$B$33,0)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H27" s="16">
         <f>IF(OR(E27="",G27=""),"",E27*G27)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -1358,7 +1358,7 @@
       <c r="G28" s="17"/>
       <c r="H28" s="18">
         <f>SUM(H13:H27)</f>
-        <v>0</v>
+        <v>694400</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -1385,7 +1385,7 @@
       <c r="G30" s="19"/>
       <c r="H30" s="20">
         <f>H28-H29</f>
-        <v>0</v>
+        <v>694400</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -1401,7 +1401,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="16">
         <f>IF(F31="별도",ROUND(H30*0.1,0),IF(F31="포함",ROUND(H30/11,0),0))</f>
-        <v>0</v>
+        <v>69440</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -1415,7 +1415,7 @@
       <c r="G32" s="17"/>
       <c r="H32" s="22">
         <f>H30+IF(F31="별도",H31,0)</f>
-        <v>0</v>
+        <v>763840</v>
       </c>
     </row>
     <row r="33" spans="2:8">
